--- a/artfynd/S 1101-2022 artfynd.xlsx
+++ b/artfynd/S 1101-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80066353</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567030</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567035</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1179,6 +1204,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567034</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195645</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195647</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1482,6 +1522,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195646</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1616,6 +1661,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80021434</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1750,6 +1800,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80021717</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1851,6 +1906,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195672</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75195673</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2062,6 +2127,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663484</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2172,6 +2242,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663485</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663487</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2392,6 +2472,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663490</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2507,6 +2592,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663494</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2613,6 +2703,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663489</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2719,6 +2814,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80663492</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2820,6 +2920,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567049</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2930,6 +3035,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88575066</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3069,6 +3179,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86491006</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3180,6 +3295,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112513403</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3297,6 +3417,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122660486</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3403,6 +3528,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128532880</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3509,6 +3639,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85567089</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3625,6 +3760,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232833</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3747,6 +3887,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126473300</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3861,6 +4006,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112178961</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3975,6 +4125,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112178907</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4081,6 +4236,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000929</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4187,6 +4347,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000745</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4293,6 +4458,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000746</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4390,8 +4560,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134613026</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>